--- a/reports/pdf_rolling5_20260916.xlsx
+++ b/reports/pdf_rolling5_20260916.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억   ·   현금 59억(1.3%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 8종목  /  매도 20종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억   ·   현금 29억(0.7%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 8종목  /  매도 20종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1351,7 +1351,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,368억   ·   현금 86억(2.5%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,368억   ·   현금 43억(1.3%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1375,7 +1375,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,483억   ·   현금 69억(2.7%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 4종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,483억   ·   현금 34억(1.4%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1573,23 +1573,23 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>켐트로닉스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-3338049000</v>
+        <v>-581166300</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>3.34%→2.10%</t>
+          <t>0.65%→0.40%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>99→60</t>
+          <t>105→66</t>
         </is>
       </c>
     </row>
@@ -1617,23 +1617,23 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>켐트로닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-581166300</v>
+        <v>-3338049000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.40%</t>
+          <t>3.34%→2.10%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>105→66</t>
+          <t>99→60</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 35억(1.8%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 3종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 17억(0.9%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1917,7 +1917,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 272억   ·   현금 2억(0.7%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 3종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 272억   ·   현금 1억(0.4%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2222,7 +2222,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억   ·   현금 9억(1.8%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억   ·   현금 4억(0.9%)      오늘 2026-09-16  vs  5일전 2026-09-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260916.xlsx
+++ b/reports/pdf_rolling5_20260916.xlsx
@@ -1104,23 +1104,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-711600000</v>
+        <v>-745200000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.74%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1132,23 +1132,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-453600000</v>
+        <v>-711600000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.18%→1.12%</t>
+          <t>1.04%→0.74%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>143→131</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1160,23 +1160,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-745200000</v>
+        <v>-453600000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.18%→1.12%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>143→131</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260916.xlsx
+++ b/reports/pdf_rolling5_20260916.xlsx
@@ -670,7 +670,7 @@
         <v>394</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3388400000</v>
+        <v>3391787248</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-74</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-519480000</v>
+        <v>-519999303</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4694400000</v>
+        <v>4699092804</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-59</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2197750000</v>
+        <v>-2199947003</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1841100000</v>
+        <v>1842940474</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-42</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1291500000</v>
+        <v>-1292791061</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>858200000</v>
+        <v>859057908</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-41</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1375550000</v>
+        <v>-1376925082</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>997100000</v>
+        <v>998096761</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1267500000</v>
+        <v>-1268767069</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>10716000000</v>
+        <v>10726712357</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-35</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-764750000</v>
+        <v>-765514490</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>921800000</v>
+        <v>922721487</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-26</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1281800000</v>
+        <v>-1283081364</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>3268800000</v>
+        <v>3272067689</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-23</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1582400000</v>
+        <v>-1583981862</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>-21</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-843150000</v>
+        <v>-843992863</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2503500000</v>
+        <v>-2506002649</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-3640000000</v>
+        <v>-3643638762</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-745200000</v>
+        <v>-712311358</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.04%→0.74%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1132,23 +1132,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-711600000</v>
+        <v>-454053446</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.74%</t>
+          <t>1.18%→1.12%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>143→131</t>
         </is>
       </c>
     </row>
@@ -1160,23 +1160,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-453600000</v>
+        <v>-745944947</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.18%→1.12%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>143→131</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
         <v>-10</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-844000000</v>
+        <v>-844843713</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1167300000</v>
+        <v>-1168466903</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>-9</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-753300000</v>
+        <v>-754053044</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>-9</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-2173500000</v>
+        <v>-2175672761</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-2271500000</v>
+        <v>-2273770728</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>-4</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-74640000</v>
+        <v>-74714615</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>115</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1546639600</v>
+        <v>1548906493</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>-224</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1500181760</v>
+        <v>-1502380560</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>41</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1282057700</v>
+        <v>1283936798</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>-78</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2508191400</v>
+        <v>-2511867629</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>35</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>7745815000</v>
+        <v>7757167957</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1573,23 +1573,23 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>켐트로닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-581166300</v>
+        <v>-3342941542</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.40%</t>
+          <t>3.34%→2.10%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>105→66</t>
+          <t>99→60</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
         <v>13</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1479735400</v>
+        <v>1481904232</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1617,23 +1617,23 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>켐트로닉스</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-3338049000</v>
+        <v>-582018109</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>3.34%→2.10%</t>
+          <t>0.65%→0.40%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>99→60</t>
+          <t>105→66</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>-37</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1736099200</v>
+        <v>-1738643782</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>-15</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1972344000</v>
+        <v>-1975234843</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>220</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>3571128000</v>
+        <v>3571129497</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>-80</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-3780880000</v>
+        <v>-3780881585</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>113</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1905971000</v>
+        <v>1905971799</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>-66</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-3912810000</v>
+        <v>-3912811640</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>60</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2170332000</v>
+        <v>2170332910</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>-63</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1247790600</v>
+        <v>-1247791123</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>39</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>182637000</v>
+        <v>182637052</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>-106</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-35690200</v>
+        <v>-35690210</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>27</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>82498500</v>
+        <v>82498524</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>-22</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-36190000</v>
+        <v>-36190010</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>49686000</v>
+        <v>49686014</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>-15</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-48142500</v>
+        <v>-48142514</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>-13</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-27891500</v>
+        <v>-27891508</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-53116000</v>
+        <v>-53116015</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>-5</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-63560000</v>
+        <v>-63560018</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260916.xlsx
+++ b/reports/pdf_rolling5_20260916.xlsx
@@ -1104,23 +1104,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-712311358</v>
+        <v>-454053446</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.74%</t>
+          <t>1.18%→1.12%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>143→131</t>
         </is>
       </c>
     </row>
@@ -1132,23 +1132,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-454053446</v>
+        <v>-712311358</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.18%→1.12%</t>
+          <t>1.04%→0.74%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>143→131</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260916.xlsx
+++ b/reports/pdf_rolling5_20260916.xlsx
@@ -1104,23 +1104,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-454053446</v>
+        <v>-712311358</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.18%→1.12%</t>
+          <t>1.04%→0.74%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>143→131</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1132,23 +1132,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-712311358</v>
+        <v>-745944947</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.74%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1160,23 +1160,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-745944947</v>
+        <v>-454053446</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.18%→1.12%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>143→131</t>
         </is>
       </c>
     </row>
@@ -1216,23 +1216,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1168466903</v>
+        <v>-2175672761</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.45%→5.38%</t>
+          <t>3.31%→2.63%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>192→183</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
@@ -1244,23 +1244,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-754053044</v>
+        <v>-1168466903</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.24%→0.99%</t>
+          <t>6.45%→5.38%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>61→52</t>
+          <t>192→183</t>
         </is>
       </c>
     </row>
@@ -1272,23 +1272,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-2175672761</v>
+        <v>-754053044</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>3.31%→2.63%</t>
+          <t>1.24%→0.99%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>61→52</t>
         </is>
       </c>
     </row>
@@ -1573,23 +1573,23 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>켐트로닉스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-3342941542</v>
+        <v>-582018109</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>3.34%→2.10%</t>
+          <t>0.65%→0.40%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>99→60</t>
+          <t>105→66</t>
         </is>
       </c>
     </row>
@@ -1617,23 +1617,23 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>켐트로닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-582018109</v>
+        <v>-3342941542</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.40%</t>
+          <t>3.34%→2.10%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>105→66</t>
+          <t>99→60</t>
         </is>
       </c>
     </row>
